--- a/data/dividends_info_20260708.xlsx
+++ b/data/dividends_info_20260708.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>58.40000152587891</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1541095850145109</v>
+        <v>0.1538724524146042</v>
       </c>
       <c r="J2" t="n">
         <v>250</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63.59999847412109</v>
+        <v>64.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.100628957223687</v>
+        <v>1.082753261374318</v>
       </c>
       <c r="J3" t="n">
         <v>229</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.680000305175781</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6198346912026306</v>
+        <v>0.6085192909653669</v>
       </c>
       <c r="J4" t="n">
         <v>159</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>58.38999938964844</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1541359837999167</v>
+        <v>0.1538724524146042</v>
       </c>
       <c r="J6" t="n">
         <v>159</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.68421067761643</v>
       </c>
       <c r="J7" t="n">
         <v>138</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.29999923706055</v>
+        <v>21.2549991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.267605679206873</v>
+        <v>1.270289393840004</v>
       </c>
       <c r="J8" t="n">
         <v>138</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I9" t="n">
-        <v>3.333333333333333</v>
+        <v>3.300330064166073</v>
       </c>
       <c r="J9" t="n">
         <v>131</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.29999923706055</v>
+        <v>21.2549991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.267605679206873</v>
+        <v>1.270289393840004</v>
       </c>
       <c r="J14" t="n">
         <v>75</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>58.38999938964844</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1541359837999167</v>
+        <v>0.1538724524146042</v>
       </c>
       <c r="J15" t="n">
         <v>75</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.016722392025687</v>
       </c>
       <c r="J16" t="n">
         <v>68</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.849999904632568</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I19" t="n">
-        <v>4.273504343171475</v>
+        <v>4.266211506894081</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.190000057220459</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="I20" t="n">
-        <v>3.34128873718614</v>
+        <v>3.373493898380374</v>
       </c>
       <c r="J20" t="n">
         <v>12</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.07199954986572</v>
+        <v>10.10200023651123</v>
       </c>
       <c r="I21" t="n">
-        <v>2.581413935860097</v>
+        <v>2.573747712460875</v>
       </c>
       <c r="J21" t="n">
         <v>12</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.47999954223633</v>
+        <v>14.57999992370605</v>
       </c>
       <c r="I22" t="n">
-        <v>4.143646539835004</v>
+        <v>4.115226358982637</v>
       </c>
       <c r="J22" t="n">
         <v>12</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.783999919891357</v>
+        <v>2.78600001335144</v>
       </c>
       <c r="I23" t="n">
-        <v>7.902299077960651</v>
+        <v>7.896625949234985</v>
       </c>
       <c r="J23" t="n">
         <v>12</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.690000057220459</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="I25" t="n">
-        <v>3.587443915504456</v>
+        <v>3.582089654213341</v>
       </c>
       <c r="J25" t="n">
         <v>12</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.95000076293945</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>1.884711707372385</v>
+        <v>1.889447272400348</v>
       </c>
       <c r="J26" t="n">
         <v>12</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.240000009536743</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I30" t="n">
-        <v>4.629629616002596</v>
+        <v>4.545454611134596</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.119999885559082</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I31" t="n">
-        <v>4.009434178699683</v>
+        <v>3.935185028814982</v>
       </c>
       <c r="J31" t="n">
         <v>-2</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>35.84999847412109</v>
+        <v>35.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4184100596497374</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="J33" t="n">
         <v>-2</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9.699999809265137</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I34" t="n">
-        <v>23.01958808150907</v>
+        <v>23.25937407575551</v>
       </c>
       <c r="J34" t="n">
         <v>-2</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.199999809265137</v>
+        <v>5.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J35" t="n">
         <v>-9</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.54000091552734</v>
+        <v>21.68000030517578</v>
       </c>
       <c r="I36" t="n">
-        <v>1.16063133414161</v>
+        <v>1.153136515133333</v>
       </c>
       <c r="J36" t="n">
         <v>-16</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.879999995231628</v>
+        <v>1.865000009536743</v>
       </c>
       <c r="I38" t="n">
-        <v>1.755319153388305</v>
+        <v>1.769436988270957</v>
       </c>
       <c r="J38" t="n">
         <v>-16</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.050000190734863</v>
+        <v>5.045000076293945</v>
       </c>
       <c r="I39" t="n">
-        <v>5.742574040532856</v>
+        <v>5.748265522585163</v>
       </c>
       <c r="J39" t="n">
         <v>-16</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.796000003814697</v>
+        <v>3.812000036239624</v>
       </c>
       <c r="I40" t="n">
-        <v>4.214963114836984</v>
+        <v>4.19727173344503</v>
       </c>
       <c r="J40" t="n">
         <v>-16</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.54800009727478</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I41" t="n">
-        <v>5.439560231894809</v>
+        <v>5.41406262101373</v>
       </c>
       <c r="J41" t="n">
         <v>-16</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>53.18999862670898</v>
+        <v>53.36999893188477</v>
       </c>
       <c r="I42" t="n">
-        <v>1.184433194708995</v>
+        <v>1.1804384721912</v>
       </c>
       <c r="J42" t="n">
         <v>-16</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.230000019073486</v>
+        <v>6.255000114440918</v>
       </c>
       <c r="I43" t="n">
-        <v>2.247191004356057</v>
+        <v>2.238209391503959</v>
       </c>
       <c r="J43" t="n">
         <v>-16</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.64999961853027</v>
+        <v>28.56999969482422</v>
       </c>
       <c r="I45" t="n">
-        <v>2.966841226239445</v>
+        <v>2.975148789217478</v>
       </c>
       <c r="J45" t="n">
         <v>-16</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>58.38999938964844</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1541359837999167</v>
+        <v>0.1538724524146042</v>
       </c>
       <c r="J46" t="n">
         <v>-16</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.399999976158142</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7142857264499277</v>
+        <v>0.6711409353016787</v>
       </c>
       <c r="J47" t="n">
         <v>-16</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.289999961853027</v>
+        <v>6.296000003814697</v>
       </c>
       <c r="I48" t="n">
-        <v>2.882352958657081</v>
+        <v>2.879606097365815</v>
       </c>
       <c r="J48" t="n">
         <v>-16</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.609999656677246</v>
+        <v>9.590000152587891</v>
       </c>
       <c r="I49" t="n">
-        <v>2.705515185105611</v>
+        <v>2.711157412545382</v>
       </c>
       <c r="J49" t="n">
         <v>-16</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10.21500015258789</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="I50" t="n">
-        <v>2.711698442117245</v>
+        <v>2.70507818546321</v>
       </c>
       <c r="J50" t="n">
         <v>-16</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.164999961853027</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I51" t="n">
-        <v>1.158798321205706</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J51" t="n">
         <v>-23</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.940000057220459</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="I52" t="n">
-        <v>3.741496525819677</v>
+        <v>3.780068617028904</v>
       </c>
       <c r="J52" t="n">
         <v>-23</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.649999976158142</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="I53" t="n">
-        <v>1.454545475563071</v>
+        <v>1.428571473173545</v>
       </c>
       <c r="J53" t="n">
         <v>-23</v>
@@ -2966,8 +2966,12 @@
           <t>IT0004093263</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>3.075000047683716</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5.20325195183402</v>
+      </c>
       <c r="J54" t="n">
         <v>-30</v>
       </c>
@@ -3010,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.824999988079071</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="I55" t="n">
-        <v>3.030303074089731</v>
+        <v>3.048780514398266</v>
       </c>
       <c r="J55" t="n">
         <v>-30</v>
@@ -3175,7 +3179,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3209,7 +3213,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3277,7 +3281,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3287,14 +3291,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3311,7 +3315,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3328,7 +3332,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3338,7 +3342,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3638,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3644,14 +3648,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3661,14 +3665,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3678,14 +3682,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3695,14 +3699,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3712,14 +3716,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3729,14 +3733,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3746,14 +3750,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,14 +3767,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3780,14 +3784,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3797,14 +3801,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3814,14 +3818,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3831,14 +3835,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3848,7 +3852,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3910,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3916,7 +3920,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3937,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3961,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3967,7 +3971,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4097,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4103,14 +4107,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4120,14 +4124,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4144,7 +4148,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4161,7 +4165,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4171,14 +4175,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4188,14 +4192,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4222,14 +4226,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4246,7 +4250,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4263,7 +4267,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4290,14 +4294,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4307,14 +4311,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4331,7 +4335,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4341,7 +4345,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4358,14 +4362,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4375,14 +4379,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4392,14 +4396,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4426,14 +4430,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4443,14 +4447,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4467,7 +4471,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4484,7 +4488,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4494,14 +4498,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4545,14 +4549,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4569,7 +4573,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4586,7 +4590,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4596,14 +4600,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4613,14 +4617,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4630,14 +4634,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4647,14 +4651,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4664,14 +4668,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4681,14 +4685,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4698,14 +4702,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4715,14 +4719,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4732,14 +4736,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4756,7 +4760,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4766,14 +4770,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4783,14 +4787,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4800,14 +4804,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4824,7 +4828,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4834,14 +4838,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4851,14 +4855,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4875,7 +4879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4885,14 +4889,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4909,7 +4913,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4919,14 +4923,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4936,14 +4940,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4953,14 +4957,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4970,14 +4974,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4987,14 +4991,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5011,7 +5015,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5028,7 +5032,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5045,7 +5049,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5062,7 +5066,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5072,14 +5076,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5089,14 +5093,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5113,7 +5117,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5123,14 +5127,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5140,14 +5144,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5164,7 +5168,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5174,14 +5178,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5191,14 +5195,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5215,7 +5219,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5232,7 +5236,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5249,7 +5253,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5259,14 +5263,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5276,14 +5280,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5300,7 +5304,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5317,7 +5321,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5327,14 +5331,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5372,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5385,7 +5389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5395,14 +5399,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5419,7 +5423,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5436,7 +5440,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5446,14 +5450,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5470,7 +5474,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5480,14 +5484,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5504,7 +5508,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5521,7 +5525,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5538,7 +5542,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5548,14 +5552,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5565,14 +5569,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5582,14 +5586,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5599,14 +5603,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5616,14 +5620,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5633,7 +5637,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5712,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5718,14 +5722,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5735,14 +5739,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5759,7 +5763,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5776,7 +5780,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5786,14 +5790,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5803,14 +5807,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5827,7 +5831,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5844,7 +5848,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5854,14 +5858,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5871,14 +5875,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5888,7 +5892,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5916,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5929,7 +5933,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5939,14 +5943,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5956,7 +5960,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5984,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5990,14 +5994,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6007,14 +6011,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6031,7 +6035,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6041,14 +6045,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6065,7 +6069,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6075,14 +6079,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6099,7 +6103,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6116,7 +6120,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6133,7 +6137,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6143,14 +6147,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6167,7 +6171,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6184,7 +6188,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6201,7 +6205,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6218,7 +6222,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6228,14 +6232,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6252,7 +6256,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6262,14 +6266,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6279,14 +6283,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6296,14 +6300,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6313,14 +6317,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6337,7 +6341,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6354,7 +6358,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6371,7 +6375,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6388,7 +6392,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6405,7 +6409,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6415,14 +6419,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6439,7 +6443,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6449,14 +6453,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6466,14 +6470,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6483,14 +6487,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6507,7 +6511,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6517,7 +6521,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6545,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6558,7 +6562,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6575,7 +6579,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6592,7 +6596,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6602,14 +6606,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6626,7 +6630,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6643,7 +6647,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6653,14 +6657,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6670,14 +6674,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6687,14 +6691,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6711,7 +6715,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6721,14 +6725,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6738,14 +6742,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6755,14 +6759,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6779,7 +6783,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6789,14 +6793,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6806,14 +6810,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6830,7 +6834,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6840,14 +6844,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6857,14 +6861,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6881,7 +6885,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6891,14 +6895,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6915,7 +6919,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6925,14 +6929,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6949,7 +6953,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6959,7 +6963,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -6974,104 +6978,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005466294</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.059454</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.48635</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7082,95 +6991,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>